--- a/output/pdf_financials_xlsx/KBRA.xlsx
+++ b/output/pdf_financials_xlsx/KBRA.xlsx
@@ -718,13 +718,13 @@
         <v>-0.018731</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.059415</v>
+        <v>-0.059415</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.280347</v>
+        <v>-0.280347</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.12008</v>
+        <v>-0.12008</v>
       </c>
     </row>
     <row r="17">
@@ -810,13 +810,13 @@
         <v>-0.018731</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.059415</v>
+        <v>-0.059415</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.280347</v>
+        <v>-0.280347</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.12008</v>
+        <v>-0.12008</v>
       </c>
     </row>
     <row r="21">
@@ -867,13 +867,13 @@
         <v>-0.018731</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.059415</v>
+        <v>-0.059415</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.280347</v>
+        <v>-0.280347</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.12008</v>
+        <v>-0.12008</v>
       </c>
     </row>
     <row r="24">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-14.01735</v>
+        <v>14.01735</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         <v>-0.018731</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.059415</v>
+        <v>-0.059415</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.280347</v>
+        <v>-0.280347</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.12008</v>
+        <v>-0.12008</v>
       </c>
     </row>
     <row r="28">
@@ -987,13 +987,13 @@
         <v>-0.018731</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.059415</v>
+        <v>-0.059415</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.280347</v>
+        <v>-0.280347</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.12008</v>
+        <v>-0.12008</v>
       </c>
     </row>
     <row r="30">
@@ -1033,13 +1033,13 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.179632</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.186906</v>
       </c>
     </row>
     <row r="93">
@@ -3370,7 +3370,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.00375</v>
       </c>
@@ -4905,13 +4909,13 @@
         </is>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.059415</v>
+        <v>-0.059415</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.280347</v>
+        <v>-0.280347</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.12008</v>
+        <v>-0.12008</v>
       </c>
     </row>
     <row r="52">

--- a/output/pdf_financials_xlsx/KBRA.xlsx
+++ b/output/pdf_financials_xlsx/KBRA.xlsx
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008541</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007745</v>
       </c>
     </row>
     <row r="13">
@@ -952,10 +952,10 @@
         <v>-0.059415</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.280347</v>
+        <v>-0.271806</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.12008</v>
+        <v>-0.112335</v>
       </c>
     </row>
     <row r="28">
@@ -990,10 +990,10 @@
         <v>-0.059415</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.280347</v>
+        <v>-0.271806</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.12008</v>
+        <v>-0.112335</v>
       </c>
     </row>
     <row r="30">
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.165903</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.038824</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.300721</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.230849</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.165903</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.038824</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.300721</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.230849</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.175903</v>
+        <v>0.01</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.142</v>
+        <v>0.103176</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.300721</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.230849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">

--- a/output/pdf_financials_xlsx/KBRA.xlsx
+++ b/output/pdf_financials_xlsx/KBRA.xlsx
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001827</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012493</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.019838</v>
@@ -4172,7 +4172,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.001827</v>
       </c>
